--- a/resources/S1_Data.xlsx
+++ b/resources/S1_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ttsigaras/Desktop/PhD/dhcp_analysis/paper/revised_figs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E18C9ED3-9BA2-9347-BC94-00FA5898798F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79052FCD-640B-D14E-A7ED-4F778B5A3CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{4EF91345-C304-6645-B673-5C1B1A1F25F8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="21">
   <si>
     <t>PMA</t>
   </si>
@@ -76,9 +76,6 @@
   </si>
   <si>
     <t>Parcel</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
   <si>
     <t>t(CoG~PMA)</t>
@@ -958,51 +955,51 @@
         <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
+      <c r="B2" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C2" s="1">
+        <v>-100</v>
+      </c>
+      <c r="D2" s="1">
+        <v>-100</v>
+      </c>
+      <c r="E2" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F2" s="1">
+        <v>-100</v>
+      </c>
+      <c r="G2" s="1">
+        <v>-100</v>
       </c>
       <c r="H2" s="1">
         <v>-100</v>
@@ -1392,23 +1389,23 @@
       <c r="A16" s="1">
         <v>16</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>13</v>
+      <c r="B16" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C16" s="1">
+        <v>-100</v>
+      </c>
+      <c r="D16" s="1">
+        <v>-100</v>
+      </c>
+      <c r="E16" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F16" s="1">
+        <v>-100</v>
+      </c>
+      <c r="G16" s="1">
+        <v>-100</v>
       </c>
       <c r="H16" s="1">
         <v>-100</v>
@@ -1421,23 +1418,23 @@
       <c r="A17" s="1">
         <v>17</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>13</v>
+      <c r="B17" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C17" s="1">
+        <v>-100</v>
+      </c>
+      <c r="D17" s="1">
+        <v>-100</v>
+      </c>
+      <c r="E17" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F17" s="1">
+        <v>-100</v>
+      </c>
+      <c r="G17" s="1">
+        <v>-100</v>
       </c>
       <c r="H17" s="1">
         <v>-100</v>
@@ -1450,23 +1447,23 @@
       <c r="A18" s="1">
         <v>18</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>13</v>
+      <c r="B18" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C18" s="1">
+        <v>-100</v>
+      </c>
+      <c r="D18" s="1">
+        <v>-100</v>
+      </c>
+      <c r="E18" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="1">
+        <v>-100</v>
+      </c>
+      <c r="G18" s="1">
+        <v>-100</v>
       </c>
       <c r="H18" s="1">
         <v>-100</v>
@@ -1537,23 +1534,23 @@
       <c r="A21" s="1">
         <v>21</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>13</v>
+      <c r="B21" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C21" s="1">
+        <v>-100</v>
+      </c>
+      <c r="D21" s="1">
+        <v>-100</v>
+      </c>
+      <c r="E21" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F21" s="1">
+        <v>-100</v>
+      </c>
+      <c r="G21" s="1">
+        <v>-100</v>
       </c>
       <c r="H21" s="1">
         <v>-100</v>
@@ -1566,23 +1563,23 @@
       <c r="A22" s="1">
         <v>22</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>13</v>
+      <c r="B22" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C22" s="1">
+        <v>-100</v>
+      </c>
+      <c r="D22" s="1">
+        <v>-100</v>
+      </c>
+      <c r="E22" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F22" s="1">
+        <v>-100</v>
+      </c>
+      <c r="G22" s="1">
+        <v>-100</v>
       </c>
       <c r="H22" s="1">
         <v>-100</v>
@@ -1595,23 +1592,23 @@
       <c r="A23" s="1">
         <v>23</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>13</v>
+      <c r="B23" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C23" s="1">
+        <v>-100</v>
+      </c>
+      <c r="D23" s="1">
+        <v>-100</v>
+      </c>
+      <c r="E23" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="1">
+        <v>-100</v>
+      </c>
+      <c r="G23" s="1">
+        <v>-100</v>
       </c>
       <c r="H23" s="1">
         <v>-100</v>
@@ -1624,23 +1621,23 @@
       <c r="A24" s="1">
         <v>24</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>13</v>
+      <c r="B24" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C24" s="1">
+        <v>-100</v>
+      </c>
+      <c r="D24" s="1">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F24" s="1">
+        <v>-100</v>
+      </c>
+      <c r="G24" s="1">
+        <v>-100</v>
       </c>
       <c r="H24" s="1">
         <v>-100</v>
@@ -1653,23 +1650,23 @@
       <c r="A25" s="1">
         <v>25</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>13</v>
+      <c r="B25" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C25" s="1">
+        <v>-100</v>
+      </c>
+      <c r="D25" s="1">
+        <v>-100</v>
+      </c>
+      <c r="E25" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F25" s="1">
+        <v>-100</v>
+      </c>
+      <c r="G25" s="1">
+        <v>-100</v>
       </c>
       <c r="H25" s="1">
         <v>-100</v>
@@ -1682,23 +1679,23 @@
       <c r="A26" s="1">
         <v>26</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>13</v>
+      <c r="B26" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C26" s="1">
+        <v>-100</v>
+      </c>
+      <c r="D26" s="1">
+        <v>-100</v>
+      </c>
+      <c r="E26" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F26" s="1">
+        <v>-100</v>
+      </c>
+      <c r="G26" s="1">
+        <v>-100</v>
       </c>
       <c r="H26" s="1">
         <v>-100</v>
@@ -1711,23 +1708,23 @@
       <c r="A27" s="1">
         <v>27</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>13</v>
+      <c r="B27" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C27" s="1">
+        <v>-100</v>
+      </c>
+      <c r="D27" s="1">
+        <v>-100</v>
+      </c>
+      <c r="E27" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="1">
+        <v>-100</v>
+      </c>
+      <c r="G27" s="1">
+        <v>-100</v>
       </c>
       <c r="H27" s="1">
         <v>-100</v>
@@ -2262,23 +2259,23 @@
       <c r="A46" s="1">
         <v>46</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>13</v>
+      <c r="B46" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C46" s="1">
+        <v>-100</v>
+      </c>
+      <c r="D46" s="1">
+        <v>-100</v>
+      </c>
+      <c r="E46" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F46" s="1">
+        <v>-100</v>
+      </c>
+      <c r="G46" s="1">
+        <v>-100</v>
       </c>
       <c r="H46" s="1">
         <v>-100</v>
@@ -2668,23 +2665,23 @@
       <c r="A60" s="1">
         <v>61</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>13</v>
+      <c r="B60" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C60" s="1">
+        <v>-100</v>
+      </c>
+      <c r="D60" s="1">
+        <v>-100</v>
+      </c>
+      <c r="E60" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F60" s="1">
+        <v>-100</v>
+      </c>
+      <c r="G60" s="1">
+        <v>-100</v>
       </c>
       <c r="H60" s="1">
         <v>-100</v>
@@ -2697,23 +2694,23 @@
       <c r="A61" s="1">
         <v>62</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>13</v>
+      <c r="B61" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C61" s="1">
+        <v>-100</v>
+      </c>
+      <c r="D61" s="1">
+        <v>-100</v>
+      </c>
+      <c r="E61" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F61" s="1">
+        <v>-100</v>
+      </c>
+      <c r="G61" s="1">
+        <v>-100</v>
       </c>
       <c r="H61" s="1">
         <v>-100</v>
@@ -2726,23 +2723,23 @@
       <c r="A62" s="1">
         <v>63</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>13</v>
+      <c r="B62" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C62" s="1">
+        <v>-100</v>
+      </c>
+      <c r="D62" s="1">
+        <v>-100</v>
+      </c>
+      <c r="E62" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F62" s="1">
+        <v>-100</v>
+      </c>
+      <c r="G62" s="1">
+        <v>-100</v>
       </c>
       <c r="H62" s="1">
         <v>-100</v>
@@ -2813,23 +2810,23 @@
       <c r="A65" s="1">
         <v>66</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>13</v>
+      <c r="B65" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C65" s="1">
+        <v>-100</v>
+      </c>
+      <c r="D65" s="1">
+        <v>-100</v>
+      </c>
+      <c r="E65" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F65" s="1">
+        <v>-100</v>
+      </c>
+      <c r="G65" s="1">
+        <v>-100</v>
       </c>
       <c r="H65" s="1">
         <v>-100</v>
@@ -2842,23 +2839,23 @@
       <c r="A66" s="1">
         <v>67</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>13</v>
+      <c r="B66" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C66" s="1">
+        <v>-100</v>
+      </c>
+      <c r="D66" s="1">
+        <v>-100</v>
+      </c>
+      <c r="E66" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F66" s="1">
+        <v>-100</v>
+      </c>
+      <c r="G66" s="1">
+        <v>-100</v>
       </c>
       <c r="H66" s="1">
         <v>-100</v>
@@ -2871,23 +2868,23 @@
       <c r="A67" s="1">
         <v>68</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>13</v>
+      <c r="B67" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C67" s="1">
+        <v>-100</v>
+      </c>
+      <c r="D67" s="1">
+        <v>-100</v>
+      </c>
+      <c r="E67" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F67" s="1">
+        <v>-100</v>
+      </c>
+      <c r="G67" s="1">
+        <v>-100</v>
       </c>
       <c r="H67" s="1">
         <v>-100</v>
@@ -2900,23 +2897,23 @@
       <c r="A68" s="1">
         <v>69</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>13</v>
+      <c r="B68" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C68" s="1">
+        <v>-100</v>
+      </c>
+      <c r="D68" s="1">
+        <v>-100</v>
+      </c>
+      <c r="E68" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F68" s="1">
+        <v>-100</v>
+      </c>
+      <c r="G68" s="1">
+        <v>-100</v>
       </c>
       <c r="H68" s="1">
         <v>-100</v>
@@ -2929,23 +2926,23 @@
       <c r="A69" s="1">
         <v>70</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>13</v>
+      <c r="B69" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C69" s="1">
+        <v>-100</v>
+      </c>
+      <c r="D69" s="1">
+        <v>-100</v>
+      </c>
+      <c r="E69" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F69" s="1">
+        <v>-100</v>
+      </c>
+      <c r="G69" s="1">
+        <v>-100</v>
       </c>
       <c r="H69" s="1">
         <v>-100</v>
@@ -2958,23 +2955,23 @@
       <c r="A70" s="1">
         <v>71</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>13</v>
+      <c r="B70" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C70" s="1">
+        <v>-100</v>
+      </c>
+      <c r="D70" s="1">
+        <v>-100</v>
+      </c>
+      <c r="E70" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F70" s="1">
+        <v>-100</v>
+      </c>
+      <c r="G70" s="1">
+        <v>-100</v>
       </c>
       <c r="H70" s="1">
         <v>-100</v>
@@ -2987,23 +2984,23 @@
       <c r="A71" s="1">
         <v>72</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>13</v>
+      <c r="B71" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C71" s="1">
+        <v>-100</v>
+      </c>
+      <c r="D71" s="1">
+        <v>-100</v>
+      </c>
+      <c r="E71" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F71" s="1">
+        <v>-100</v>
+      </c>
+      <c r="G71" s="1">
+        <v>-100</v>
       </c>
       <c r="H71" s="1">
         <v>-100</v>
